--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -1266,18 +1266,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>cuh.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>foi.contact@addenbrookes.nhs.uk</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.cuh.nhs.uk/about-us/freedom-information/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CUH FOI page returned 404; FOI process exists but specific email not confirmed; CUH contact page lists only phone numbers; FOI sub-pages 404 across multiple paths.</t>
+          <t>CUH FOI page returned 404; FOI process exists but specific email not confirmed; CUH contact page lists only phone numbers; FOI sub-pages 404 across multiple paths.; FOI primary updated 2026-05-16 from https://www.cuh.nhs.uk/about-us/freedom-information/; prior value moved to _alt</t>
         </is>
       </c>
     </row>
@@ -5061,13 +5065,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>nuhnt.nuhmedia@nhs.net</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>NUHMedia@nuh.nhs.uk</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.nuh.nhs.uk/media-enquiries/</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5087,7 +5095,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Nottingham UH: contact-us, comms and news-media URLs all 404; no public press email surfaced.</t>
+          <t>Nottingham UH: contact-us, comms and news-media URLs all 404; no public press email surfaced.; press primary updated 2026-05-16 from https://www.nuh.nhs.uk/media-enquiries/; prior value moved to _alt</t>
         </is>
       </c>
     </row>
@@ -8002,16 +8010,24 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
+          <t>ncm.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
           <t>whh.foi@nhs.net</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
           <t>https://northcheshireandmersey.nhs.uk/about-us/freedom-of-information/</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>FOI primary updated 2026-05-16 from https://northcheshireandmersey.nhs.uk/about-us/freedom-of-information/; prior value moved to _alt</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -8539,7 +8539,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>added 2026-05-16; new entity Apr 2026; board papers URL TBD</t>
+          <t>Shadow / pre-legal trust as of 2026-05-16. ODS operational date 2026-04-07; legal establishment date 2026-06-01. No public website, press office or FOI process yet. Registered address is DHSC HQ (Wellington House, 133-155 Waterloo Road, London SE1 8UG). Until the trust is operational with patients (expected 2027), route press enquiries via NHS England press office (nhsengland.media@nhs.net) and FOI requests via NHS England (england.contactus@nhs.net) or DHSC.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -2276,10 +2276,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>pressoffice@enherts-tr.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>communications.enh-tr@nhs.net</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>https://www.enherts-tr.nhs.uk/contact/</t>
@@ -2298,7 +2302,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Both emails obscured by Cloudflare email-protection on the pages</t>
+          <t>Both emails obscured by Cloudflare email-protection on the pages | press primary updated 2026-05-29 from [https://www.enherts-tr.nhs.uk/contact/]; prior value communications.enh-tr@nhs.net moved to _alt</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5541,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>rf-tr.mediaenquiries@nhs.net</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>tr-rf.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>rf.mediaenquiries@nhs.net</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5563,7 +5567,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Site (incl FOI page) returned 403 to scraping; press email confirmed via search results. FOI email not extractable - likely rf-tr.foi@nhs.net but unverified; Royal Free FOI page returned 403 to WebFetch on multiple attempts; could not retrieve email.</t>
+          <t>Site (incl FOI page) returned 403 to scraping; press email confirmed via search results. FOI email not extractable - likely rf-tr.foi@nhs.net but unverified; Royal Free FOI page returned 403 to WebFetch on multiple attempts; could not retrieve email. | press primary updated 2026-05-29 from [https://www.royalfree.nhs.uk/contact-us/contact-media-team]; prior value tr-rf.communications@nhs.net moved to _alt</t>
         </is>
       </c>
     </row>
@@ -5864,14 +5868,14 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
+          <t>shpu@infreemation.co.uk</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
           <t>shsc@infreemation.co.uk</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>foi@shsc.nhs.uk</t>
-        </is>
-      </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>https://www.sheffieldpartnership.nhs.uk/contact-us/freedom-information-requests</t>
@@ -5879,7 +5883,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Sheffield Health &amp; Social Care rebranded as Sheffield Partnership University FT; FOI uses Infreemation portal</t>
+          <t>Sheffield Health &amp; Social Care rebranded as Sheffield Partnership University FT; FOI uses Infreemation portal | foi primary updated 2026-05-29 from [https://www.sheffieldpartnership.nhs.uk/contact-us/freedom-information-requests]; prior value shsc@infreemation.co.uk moved to _alt</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -760,14 +760,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>communications@bedsft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>communications@bedfordhospital.nhs.uk</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>communications@ldh.nhs.uk</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>https://www.bedfordshirehospitals.nhs.uk/contact-us/media-enquiries/</t>
@@ -790,7 +790,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Trust runs two press inboxes: communications@bedfordhospital.nhs.uk and communications@ldh.nhs.uk (Luton &amp; Dunstable site)</t>
+          <t>Trust runs two press inboxes: communications@bedfordhospital.nhs.uk and communications@ldh.nhs.uk (Luton &amp; Dunstable site) | press primary updated 2026-06-06 from https://www.bedfordshirehospitals.nhs.uk/contact-us/media-enquiries/ (unified communications@bedsft.nhs.uk now shown on page); prior primary communications@bedfordhospital.nhs.uk moved to _alt; legacy communications@ldh.nhs.uk retired (one alt slot).</t>
         </is>
       </c>
     </row>
@@ -4325,12 +4325,12 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.mpft.nhs.uk/about-us/freedom-information</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>MPFT FOI page directs requests via postal address or online portal (mpft.ams-sar.com); no FOI email published.</t>
+          <t>MPFT FOI page directs requests via postal address or online portal (mpft.ams-sar.com); no FOI email published. | foi_source_url set 2026-06-06 from live FOI page (no email published; FOI via online Access Request Portal); existing foi@mpft.nhs.uk retained.</t>
         </is>
       </c>
     </row>
@@ -4407,12 +4407,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.moorfields.nhs.uk/about-us/freedom-of-information</t>
+          <t>https://www.moorfields.nhs.uk/about-us/resources/freedom-of-information</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>FOI page lists webrequests inbox; may be IG-handled rather than dedicated FOI</t>
+          <t>FOI page lists webrequests inbox; may be IG-handled rather than dedicated FOI | foi_source_url corrected 2026-06-06 (old about-us/freedom-of-information now 404); live page shows moorfields.fois@nhs.net (= existing _alt); primary Moorfields.webrequests@nhs.net retained.</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.ncic.nhs.uk/patients-visitors/patient-information-leaflets/freedom-information</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>FOI page not located; North Cumbria FOI URLs all 404; contact page references FOI but only via submission portal.</t>
+          <t>FOI page not located; North Cumbria FOI URLs all 404; contact page references FOI but only via submission portal. | foi_source_url located 2026-06-06; live page confirms FOIRequests@ncic.nhs.uk (matches primary).</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.sussexcommunity.nhs.uk/contact-us/press-and-media</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6662,12 +6662,12 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.sussexcommunity.nhs.uk/contact-us/freedom-of-information</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Both press and FOI pages returned 403 on direct fetch; emails are spam-obfuscated on the site. IG team based at Brighton General Hospital; Sussex Community: both press-and-media and FOI URLs returned 403 to WebFetch.</t>
+          <t>Both press and FOI pages returned 403 on direct fetch; emails are spam-obfuscated on the site. IG team based at Brighton General Hospital; Sussex Community: both press-and-media and FOI URLs returned 403 to WebFetch. | source URLs set 2026-06-06 via Playwright render; press scftcommunications@nhs.net and foi sc-tr.freedomofinformation@nhs.net both confirmed on-page (match primaries).</t>
         </is>
       </c>
     </row>
